--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.1.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.1.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="110">
-  <si>
-    <t>Загрузочный лист 5.1.1 (Время печати: 27.05.2026 19:51:40)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+  <si>
+    <t>Загрузочный лист 5.1.1 (Время печати: 28.05.2026 17:37:19)</t>
   </si>
   <si>
     <t>Бисёр Маркэт  (b7_848)</t>
@@ -837,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AQ85"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1350,9 +1350,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13"/>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
+      <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -1603,9 +1601,7 @@
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="13"/>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
+      <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
@@ -1908,7 +1904,7 @@
       <c r="C19" s="12"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -2613,9 +2609,7 @@
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="13"/>
-      <c r="E33" s="13">
-        <v>14</v>
-      </c>
+      <c r="E33" s="13"/>
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
@@ -2968,9 +2962,7 @@
       </c>
       <c r="C40" s="12"/>
       <c r="D40" s="13"/>
-      <c r="E40" s="13">
-        <v>465</v>
-      </c>
+      <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
@@ -3323,9 +3315,7 @@
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="13"/>
-      <c r="E47" s="13">
-        <v>183</v>
-      </c>
+      <c r="E47" s="13"/>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
@@ -3576,9 +3566,7 @@
       </c>
       <c r="C52" s="12"/>
       <c r="D52" s="13"/>
-      <c r="E52" s="13">
-        <v>0</v>
-      </c>
+      <c r="E52" s="13"/>
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
@@ -3676,9 +3664,7 @@
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="13"/>
-      <c r="E54" s="13">
-        <v>32</v>
-      </c>
+      <c r="E54" s="13"/>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
@@ -3929,9 +3915,7 @@
       </c>
       <c r="C59" s="12"/>
       <c r="D59" s="13"/>
-      <c r="E59" s="13">
-        <v>0</v>
-      </c>
+      <c r="E59" s="13"/>
       <c r="F59" s="13"/>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
@@ -4519,45 +4503,123 @@
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="3"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-      <c r="W71" s="17"/>
-      <c r="X71" s="17"/>
-      <c r="Y71" s="17"/>
-      <c r="Z71" s="17"/>
-      <c r="AA71" s="17"/>
-      <c r="AB71" s="17"/>
-      <c r="AC71" s="17"/>
-      <c r="AD71" s="17"/>
-      <c r="AE71" s="17"/>
-      <c r="AF71" s="17"/>
-      <c r="AG71" s="17"/>
-      <c r="AH71" s="17"/>
-      <c r="AI71" s="17"/>
-      <c r="AJ71" s="17"/>
-      <c r="AK71" s="17"/>
-      <c r="AL71" s="17"/>
-      <c r="AM71" s="17"/>
-      <c r="AN71" s="17"/>
-      <c r="AO71" s="17"/>
-      <c r="AP71" s="17"/>
-      <c r="AQ71" s="17"/>
+      <c r="E71" s="17">
+        <v>939</v>
+      </c>
+      <c r="F71" s="17">
+        <v>16</v>
+      </c>
+      <c r="G71" s="17">
+        <v>6</v>
+      </c>
+      <c r="H71" s="17">
+        <v>20</v>
+      </c>
+      <c r="I71" s="17">
+        <v>40</v>
+      </c>
+      <c r="J71" s="17">
+        <v>3</v>
+      </c>
+      <c r="K71" s="17">
+        <v>8</v>
+      </c>
+      <c r="L71" s="17">
+        <v>24</v>
+      </c>
+      <c r="M71" s="17">
+        <v>20</v>
+      </c>
+      <c r="N71" s="17">
+        <v>0</v>
+      </c>
+      <c r="O71" s="17">
+        <v>12</v>
+      </c>
+      <c r="P71" s="17">
+        <v>180</v>
+      </c>
+      <c r="Q71" s="17">
+        <v>22</v>
+      </c>
+      <c r="R71" s="17">
+        <v>64</v>
+      </c>
+      <c r="S71" s="17">
+        <v>16</v>
+      </c>
+      <c r="T71" s="17">
+        <v>25</v>
+      </c>
+      <c r="U71" s="17">
+        <v>21</v>
+      </c>
+      <c r="V71" s="17">
+        <v>6</v>
+      </c>
+      <c r="W71" s="17">
+        <v>22</v>
+      </c>
+      <c r="X71" s="17">
+        <v>6</v>
+      </c>
+      <c r="Y71" s="17">
+        <v>20</v>
+      </c>
+      <c r="Z71" s="17">
+        <v>16</v>
+      </c>
+      <c r="AA71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AB71" s="17">
+        <v>28</v>
+      </c>
+      <c r="AC71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AD71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AE71" s="17">
+        <v>12</v>
+      </c>
+      <c r="AF71" s="17">
+        <v>8</v>
+      </c>
+      <c r="AG71" s="17">
+        <v>24</v>
+      </c>
+      <c r="AH71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AI71" s="17">
+        <v>80</v>
+      </c>
+      <c r="AJ71" s="17">
+        <v>16</v>
+      </c>
+      <c r="AK71" s="17">
+        <v>8</v>
+      </c>
+      <c r="AL71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AM71" s="17">
+        <v>40</v>
+      </c>
+      <c r="AN71" s="17">
+        <v>20</v>
+      </c>
+      <c r="AO71" s="17">
+        <v>24</v>
+      </c>
+      <c r="AP71" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="17">
+        <v>32</v>
+      </c>
     </row>
     <row r="72" ht="60" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
@@ -4568,45 +4630,119 @@
       <c r="D72" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
+      <c r="E72" s="22">
+        <v>11676900</v>
+      </c>
+      <c r="F72" s="21">
+        <v>154800</v>
+      </c>
+      <c r="G72" s="21">
+        <v>153000</v>
+      </c>
+      <c r="H72" s="21">
+        <v>193500</v>
+      </c>
+      <c r="I72" s="21">
+        <v>387000</v>
+      </c>
+      <c r="J72" s="21">
+        <v>76500</v>
+      </c>
+      <c r="K72" s="21">
+        <v>294000</v>
+      </c>
+      <c r="L72" s="21">
+        <v>384400</v>
+      </c>
+      <c r="M72" s="21">
+        <v>207000</v>
+      </c>
       <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
-      <c r="R72" s="21"/>
-      <c r="S72" s="21"/>
-      <c r="T72" s="21"/>
-      <c r="U72" s="21"/>
-      <c r="V72" s="21"/>
-      <c r="W72" s="21"/>
-      <c r="X72" s="21"/>
-      <c r="Y72" s="21"/>
-      <c r="Z72" s="21"/>
-      <c r="AA72" s="21"/>
-      <c r="AB72" s="21"/>
-      <c r="AC72" s="21"/>
-      <c r="AD72" s="21"/>
-      <c r="AE72" s="21"/>
-      <c r="AF72" s="21"/>
-      <c r="AG72" s="21"/>
-      <c r="AH72" s="21"/>
-      <c r="AI72" s="21"/>
-      <c r="AJ72" s="21"/>
-      <c r="AK72" s="21"/>
-      <c r="AL72" s="21"/>
-      <c r="AM72" s="21"/>
-      <c r="AN72" s="21"/>
-      <c r="AO72" s="21"/>
+      <c r="O72" s="21">
+        <v>116100</v>
+      </c>
+      <c r="P72" s="21">
+        <v>2318000</v>
+      </c>
+      <c r="Q72" s="21">
+        <v>203800</v>
+      </c>
+      <c r="R72" s="21">
+        <v>619200</v>
+      </c>
+      <c r="S72" s="21">
+        <v>154800</v>
+      </c>
+      <c r="T72" s="21">
+        <v>577500</v>
+      </c>
+      <c r="U72" s="21">
+        <v>538800</v>
+      </c>
+      <c r="V72" s="21">
+        <v>153000</v>
+      </c>
+      <c r="W72" s="21">
+        <v>209200</v>
+      </c>
+      <c r="X72" s="21">
+        <v>115500</v>
+      </c>
+      <c r="Y72" s="21">
+        <v>193500</v>
+      </c>
+      <c r="Z72" s="21">
+        <v>154800</v>
+      </c>
+      <c r="AA72" s="21">
+        <v>193500</v>
+      </c>
+      <c r="AB72" s="21">
+        <v>270900</v>
+      </c>
+      <c r="AC72" s="21">
+        <v>714000</v>
+      </c>
+      <c r="AD72" s="21">
+        <v>207000</v>
+      </c>
+      <c r="AE72" s="21">
+        <v>116100</v>
+      </c>
+      <c r="AF72" s="21">
+        <v>77400</v>
+      </c>
+      <c r="AG72" s="21">
+        <v>240300</v>
+      </c>
+      <c r="AH72" s="21">
+        <v>193500</v>
+      </c>
+      <c r="AI72" s="21">
+        <v>774000</v>
+      </c>
+      <c r="AJ72" s="21">
+        <v>165600</v>
+      </c>
+      <c r="AK72" s="21">
+        <v>77400</v>
+      </c>
+      <c r="AL72" s="21">
+        <v>193500</v>
+      </c>
+      <c r="AM72" s="21">
+        <v>387000</v>
+      </c>
+      <c r="AN72" s="21">
+        <v>510000</v>
+      </c>
+      <c r="AO72" s="21">
+        <v>240300</v>
+      </c>
       <c r="AP72" s="21"/>
-      <c r="AQ72" s="21"/>
+      <c r="AQ72" s="21">
+        <v>112000</v>
+      </c>
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
@@ -5375,6 +5511,6 @@
     <mergeCell ref="B85:C85"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>